--- a/tools/importer/reports/import-products.report.xlsx
+++ b/tools/importer/reports/import-products.report.xlsx
@@ -64,13 +64,13 @@
     <t>products.report.json</t>
   </si>
   <si>
-    <t>["hero-fullbleed","hero-fullbleed","cards-product","cards-product","cards-insights","cards-insights"]</t>
+    <t>["hero-fullbleed","hero-fullbleed","cards-product","cards-product","cards-insights"]</t>
   </si>
   <si>
     <t>products</t>
   </si>
   <si>
-    <t>2026-08-26T20:12:47.932Z</t>
+    <t>2026-08-26T20:35:34.948Z</t>
   </si>
   <si>
     <t>Products</t>
